--- a/Result/checksun_type/石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等).xlsx
+++ b/Result/checksun_type/石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>11.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5879635.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>8335142.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>8335142.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>14613549.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>14489321.8</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>14489321.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1722351.154282046</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5879635</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5879635.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>11.77</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12.16</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>8171585.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>9503120.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>9503120.800000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>17828595.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14848825.04</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14848825.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1386977.371015554</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>8171585</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>8171585.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>11.81</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>12.05</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>12.17</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>10731727.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10988901.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10988901.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>17757653.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>15014653.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>15014653.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1103903.131670011</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>10731727</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>10731727.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>11.93</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>12.08</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>11166579.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>11493180.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>11493180.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17467849.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14954756.84</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>14954756.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-934387.1779024508</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>11166579</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>11166579.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>12.09</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>5726185.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>13205420.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>13205420.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>17756818.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14855487.32</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>14855487.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-705441.8447379898</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5726185</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5726185.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>12.25</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>12.12</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>11719528.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>20891956.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>20891956</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>18961046.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14956059.6</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>14956059.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>229716.6256661713</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>11719528</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>11719528.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>12.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>15600488.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>26154070.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>26154070.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>18970398.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>14861689.48</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>14861689.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>915309.2396126054</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>15600488</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>15600488.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>12.43</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>12.21</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>13253121.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>24526404.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>24526404.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>18413952.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14695067.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>14695067.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1446220.500978492</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>13253121</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>13253121.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>12.36</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>19727782.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>23442518.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>23442518.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>18836267.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>14598483.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>14598483.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2404518.03503767</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>19727782</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>19727782.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>12.27</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>44158861.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>22308216.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>22308216.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>18771135.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>14357926.64</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>14357926.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2993925.189585157</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>44158861</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>44158861.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>12.15</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>38030102.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>17030137.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>17030137.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>16553492.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13667025.36</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13667025.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1111393.903596381</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>38030102</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>38030102.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>28.06</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>27.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>216494090.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>373212445.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>373212445</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>336737167.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>234328828.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>234328828.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>18222201.05117249</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>216494090</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>216494090.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>28.08</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>27.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>180939331.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>374481984.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>374481984</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>351608160.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>232392437.72</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>232392437.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>33124129.80586833</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>180939331</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>180939331.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>28.07</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>27.34</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>27.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>904973262.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>406724156.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>406724156</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>349033740.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>231625338.32</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>231625338.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>57039033.28379565</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>904973262</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>904973262.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>28.11</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>27.31</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>27.47</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>27.47</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>316742630.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>304952494.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>304952494</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>277539104.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>216932492.5</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>216932492.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>11591008.74212769</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>316742630</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>316742630.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>28.01</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>27.28</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>246912912.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>286432675.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>286432675.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>272296602.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>212371753.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>212371753.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>9276005.370383173</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>246912912</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>246912912.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>27.95</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>27.24</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>27.45</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>27.45</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>222841785.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>300261890.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>300261890</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>261983138.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>210678920.72</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>210678920.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>13119327.29037741</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>222841785</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>222841785.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>27.86</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>27.2</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27.44</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>342150191.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>328734337.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>328734337</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>260445450.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>209474373.76</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>209474373.76</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>20720289.09428424</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>342150191</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>342150191.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>27.68</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>27.15</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27.43</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>396114952.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>291343324.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>291343324.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>249678133.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>204549594.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>204549594.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>18055752.13221243</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>396114952</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>396114952.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>27.42</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>27.41</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27.41</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>224143536.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>250125714.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>250125714.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>231978485.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>199521107.72</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>199521107.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>7822483.788816571</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>224143536</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>224143536.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>27.17</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>27.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>316058986.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>258160530.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>258160530.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>242525631.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>200755778.86</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>200755778.86</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>11349663.44865048</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>316058986</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>316058986.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>26.99</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>27.39</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>365204020.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>223704386.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>223704386.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>240175645.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>198426149.68</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>198426149.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>6135062.482389957</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>365204020</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>365204020.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>31.88</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>30</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>398780549.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>593348955.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>593348955.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1182774146.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>558033656.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>558033656.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-61585052.20607018</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>398780549</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>398780549.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>31.9</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>31.03</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>29.94</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>29.94</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>573811576.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>639140958.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>639140958</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1298204859.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>556181619.44</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>556181619.4400001</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-29185675.31124961</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>573811576</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>573811576.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>32.31</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>29.9</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>617869280.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>713943389.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>713943389.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1385381878.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>548956919.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>548956919.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-611829.9503898621</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>617869280</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>617869280.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>32.72</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>601484505.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>790120467.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>790120467.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1381540589.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>540487513.94</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>540487513.9400001</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>35509331.92049515</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>601484505</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>601484505.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>33.14</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>30.9</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>29.77</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>29.77</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>774798868.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1224630852.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1224630852.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1381352592.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>530923291.02</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>530923291.02</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>87598312.91745603</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>774798868</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>774798868.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>33.64</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>29.68</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>29.68</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>627740561.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1772199337.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1772199337</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1333371150.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>519334570.38</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>519334570.38</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>140313235.7017767</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>627740561</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>627740561.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>33.78</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.63</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29.63</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>947823733.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1957268760.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1957268760.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1319896902.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>510864125.42</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>510864125.42</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>226365328.4400284</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>947823733</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>947823733.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>30.49</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.54</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.54</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>998754669.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>2056820368.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>2056820368.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1250860855.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>499842523.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>499842523.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>306917787.9075298</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>998754669</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>998754669.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>32.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.45</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2774036430.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1972960711.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1972960711.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1174625268.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>494079808.74</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>494079808.74</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>405574494.4358344</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2774036430</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2774036430.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>31.42</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.38</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.38</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>3512641292.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1538074331.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1538074331.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>941548438.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>446722181.38</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>446722181.38</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>341819083.1392757</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3512641292</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3512641292.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>29.98</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.26</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.26</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1553087678.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>894542963.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>894542963.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>612270209.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>385550752.82</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>385550752.82</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>159395864.5320747</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1553087678</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1553087678.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>8.185999999999998</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>8.42</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>7.75</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>190104107.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>227511087.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>227511087</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>393183371.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>355153164.84</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>355153164.84</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-104647650.2770334</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>190104107</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>190104107.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>8.197999999999999</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>8.39</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>7.74</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>7.74</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>238961215.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>257581143.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>257581143.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>455894719.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>354625836.96</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>354625836.96</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-99213883.10816532</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>238961215</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>238961215.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>8.306000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>8.36</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>7.73</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>255851037.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>276242629.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>276242629.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>506180540.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>354303174.1</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>354303174.1</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-93142695.75591934</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>255851037</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>255851037.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>8.434000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>7.72</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>211248015.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>306801071.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>306801071.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>621514548.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>355007411.92</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>355007411.92</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-82952669.90428513</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>211248015</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>211248015.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>8.564</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>8.28</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>7.71</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>7.71</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>241391061.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>391776782.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>391776782.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>978843665.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>356730700.62</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>356730700.62</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-60653999.548226</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>241391061</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>241391061.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>8.656</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>8.23</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>7.69</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>340454391.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>558855655.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>558855655.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1068661306.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>353040026.6</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>353040026.6</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-29862153.98427641</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>340454391</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>340454391.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>8.716</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>8.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>7.67</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>7.67</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>332268645.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>654208294.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>654208294.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1260074352.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>347911102.96</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>347911102.96</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>4578774.106518507</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>332268645</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>332268645.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>8.676</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>8.12</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>7.64</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>7.64</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>408643247.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>736118452.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>736118452</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1272038677.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>343497631.72</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>343497631.72</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>54493616.51813579</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>408643247</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>408643247.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>8.658</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>8.05</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>7.61</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>636126570.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>936228024.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>936228024.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1243486675.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>336405493.04</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>336405493.04</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>115671340.5876557</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>636126570</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>636126570.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>8.76</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>7.57</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1076785424.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1565910548.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1565910548.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1194820596.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>324668285.26</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>324668285.26</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>174563756.7731249</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1076785424</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1076785424.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>8.934000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>7.54</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>817217586.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1578466958.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1578466958</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1099347016.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>304334645.6</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>304334645.6</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>205247911.3676121</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>817217586</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>817217586.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3512622548</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>6744255965</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>4850127005</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>4661687858</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>10708653199</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>7717712495</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>13894804772</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>12606646015</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>12847401961</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>17904603214</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>8385497650</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>40.04</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>39.79</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>38.9</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>504202980.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>843671193.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>843671193.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1432628587.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>817449144.5</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>817449144.5</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-66364592.2718823</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>504202980</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>504202980.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>40.15</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>39.77</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>38.86</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>38.86</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1191410722.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1001140841.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1001140841</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1612190852.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>817981984.0</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>817981984</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-14108799.98412943</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1191410722</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1191410722.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>40.67</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>39.81</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>38.84</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>38.84</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>757743633.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1081544530.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1081544530.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1662546115.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>801871651.48</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>801871651.48</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-12583183.35933495</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>757743633</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>757743633.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>41.19</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>38.8</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>827539453.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1292858575.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1292858575.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1651121749.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>795921301.56</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>795921301.5599999</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>36509999.33177662</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>827539453</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>827539453.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>41.7</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>39.8</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>38.76</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>38.76</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>937459181.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1458881861.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1458881861.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1666154267.0</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>785879279.18</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>785879279.1799999</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>97861065.3429439</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>937459181</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>937459181.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>41.97000000000001</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>39.68</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>38.69</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>38.69</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1291551216.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>2021585981.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>2021585981</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1636934660.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>778694570.54</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>778694570.54</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>170233293.5966489</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1291551216</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1291551216.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>42.23</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>38.65</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1593429169.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>2223240863.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>2223240863.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1628447057.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>760096745.28</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>760096745.28</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>229603998.2949185</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1593429169</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1593429169.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>41.91</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>39.47</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>38.58</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>38.58</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1814313857.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2243547701.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2243547701.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1527257594.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>737882950.9</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>737882950.9</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>273875081.531914</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1814313857</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1814313857.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>41.09</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>39.26</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>38.48</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>38.48</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1657655883.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2009384923.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2009384923.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1400414235.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>713699684.46</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>713699684.46</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>303672016.6729105</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1657655883</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1657655883.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>40.3</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>39.0</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>38.4</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3750979780.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1873426672.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1873426672.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1308948214.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>694282279.54</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>694282279.54</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>352178420.6360159</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3750979780</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3750979780.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>39.23999999999999</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>38.72</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>38.33</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2299825630.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1252283340.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1252283340.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>976594682.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>634083400.12</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>634083400.12</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>184610779.4534516</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2299825630</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2299825630.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>

--- a/Result/checksun_type/石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等).xlsx
+++ b/Result/checksun_type/石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等).xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-54.18</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>6906658.319217284</t>
+          <t>6906658.319217275</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-52.31</t>
+          <t>-51.75</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>8126810.664161487</t>
+          <t>8126810.664161476</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-50.77</t>
+          <t>-50.19</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>9120483.849272715</t>
+          <t>9120483.849272702</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-51.51</t>
+          <t>-50.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>9583441.822488755</t>
+          <t>9583441.82248874</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-54.85</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>9339540.0828817</t>
+          <t>9339540.082881682</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-60.92</t>
+          <t>-60.46</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>7898414.758414956</t>
+          <t>7898414.758414935</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-67.18</t>
+          <t>-66.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>5226461.610555548</t>
+          <t>5226461.610555524</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-71.85</t>
+          <t>-71.52</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1592549.591032912</t>
+          <t>1592549.591032883</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>5526636.865558766</t>
+          <t>5526636.865558758</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-74.00</t>
+          <t>-73.69</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>877260.9956645744</t>
+          <t>877260.9956645423</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-1098361.275884446</t>
+          <t>-1098361.275884453</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-72.36</t>
+          <t>-72.03</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1236465.045037124</t>
+          <t>1236465.045037087</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-584714.0395217277</t>
+          <t>-584714.0395217389</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-71.21</t>
+          <t>-70.86</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>39445079.27689243</t>
+          <t>37518791.19094488</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1567588.514956915</t>
+          <t>1567588.514956874</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>201308.5138364993</t>
+          <t>201308.5138364881</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>化學工業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-93.95</t>
+          <t>-95.28</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>12083455.37605909</t>
+          <t>12083455.37605972</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3572218.541093975</t>
+          <t>-3572218.541093886</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-93.14</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>14929941.54281419</t>
+          <t>14929941.54281492</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>6394736.020611554</t>
+          <t>6394736.020611674</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-90.23</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>16481797.09230558</t>
+          <t>16481797.09230642</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>19052313.50088334</t>
+          <t>19052313.50088349</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-84.15</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>16014430.47256416</t>
+          <t>16014430.47256513</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>26328251.91909716</t>
+          <t>26328251.91909733</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-81.89</t>
+          <t>-85.86</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>14139190.20955817</t>
+          <t>14139190.20955928</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>18687936.80514923</t>
+          <t>18687936.80514944</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9169,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-81.28</t>
+          <t>-85.37</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>13312145.37399616</t>
+          <t>13312145.37399743</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>22277073.8636111</t>
+          <t>22277073.86361134</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-81.33</t>
+          <t>-85.41</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>11682158.37588435</t>
+          <t>11682158.37588581</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>25058545.9877134</t>
+          <t>25058545.98771366</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-82.15</t>
+          <t>-86.06</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>9250087.901006341</t>
+          <t>9250087.90100802</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>20449571.66544122</t>
+          <t>20449571.66544154</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-84.08</t>
+          <t>-87.56</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>7213818.125654546</t>
+          <t>7213818.125656469</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>5287999.074143738</t>
+          <t>5287999.074144125</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-84.31</t>
+          <t>-87.75</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>7563967.044111055</t>
+          <t>7563967.044113258</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>10634197.33392796</t>
+          <t>10634197.33392841</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-07-09 00:00:00</t>
+          <t>2025-07-10 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-85.85</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>422346204.62749</t>
+          <t>487556202.7795275</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>7005743.355053436</t>
+          <t>7005743.355055958</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>19187494.8716937</t>
+          <t>19187494.87169421</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>260544675.9083902</t>
+          <t>260544675.9083903</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>282951195.1903455</t>
+          <t>282951195.1903456</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>291732661.897406</t>
+          <t>291732661.8974063</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>273184227.3080002</t>
+          <t>273184227.3080005</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>223671158.0441188</t>
+          <t>223671158.0441191</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>161413253.8390831</t>
+          <t>161413253.8390834</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="CP29" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ29" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>98903580.224516</t>
+          <t>98903580.2245164</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="CP30" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ30" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>50178294.01005173</t>
+          <t>50178294.01005223</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>92380396.1537348</t>
+          <t>92380396.15373492</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="CP31" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ31" t="inlineStr">
@@ -15846,12 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16168,12 +16168,12 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>42505184.52938208</t>
+          <t>42505184.52938265</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>23472831.96919537</t>
+          <t>23472831.96919549</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="CP32" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ32" t="inlineStr">
@@ -16343,12 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>45965612.26759785</t>
+          <t>45965612.26759849</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>27220593.02809608</t>
+          <t>27220593.0280962</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS33" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="CP33" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ33" t="inlineStr">
@@ -16840,12 +16840,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>846860650.2908367</t>
+          <t>688676987.9852362</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -17162,12 +17162,12 @@
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>49373797.5838709</t>
+          <t>49373797.58387165</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>34441201.36123669</t>
+          <t>34441201.36123681</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="CP34" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ34" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -17618,12 +17618,12 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>-90.66</t>
+          <t>-90.78</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -17659,12 +17659,12 @@
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>5783611.794879476</t>
+          <t>5783611.794879261</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t>-10269897.46030781</t>
+          <t>-10269897.4603079</t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="CP35" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ35" t="inlineStr">
@@ -17834,12 +17834,12 @@
       </c>
       <c r="CX35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -18115,12 +18115,12 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>-88.33</t>
+          <t>-88.49</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
@@ -18156,12 +18156,12 @@
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>8702431.659458982</t>
+          <t>8702431.659458745</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>-4510397.721784681</t>
+          <t>-4510397.72178477</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="CP36" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ36" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="CX36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
@@ -18612,12 +18612,12 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>-85.51</t>
+          <t>-85.70</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
@@ -18653,12 +18653,12 @@
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>11104764.27423056</t>
+          <t>11104764.27423029</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>4466878.430454969</t>
+          <t>4466878.43045488</t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="CP37" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ37" t="inlineStr">
@@ -18828,12 +18828,12 @@
       </c>
       <c r="CX37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -18895,7 +18895,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -19109,12 +19109,12 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>-83.53</t>
+          <t>-83.75</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -19150,12 +19150,12 @@
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>12311652.60946248</t>
+          <t>12311652.60946219</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t>11662196.27542391</t>
+          <t>11662196.27542382</t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="CP38" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ38" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>-83.10</t>
+          <t>-83.32</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>12429735.57928768</t>
+          <t>12429735.57928734</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>18551181.50840011</t>
+          <t>18551181.50840002</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="CP39" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ39" t="inlineStr">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="CX39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -20103,12 +20103,12 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-84.08</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
@@ -20144,12 +20144,12 @@
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>11316745.41035814</t>
+          <t>11316745.41035777</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>24903446.78735185</t>
+          <t>24903446.78735176</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="CP40" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ40" t="inlineStr">
@@ -20319,12 +20319,12 @@
       </c>
       <c r="CX40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20386,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -20600,12 +20600,12 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>-85.27</t>
+          <t>-85.47</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -20641,12 +20641,12 @@
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>8846436.06908656</t>
+          <t>8846436.06908613</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>27784669.97916317</t>
+          <t>27784669.97916308</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="CP41" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ41" t="inlineStr">
@@ -20816,12 +20816,12 @@
       </c>
       <c r="CX41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
@@ -21097,12 +21097,12 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>-86.95</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -21138,12 +21138,12 @@
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>5403120.812708993</t>
+          <t>5403120.812708504</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>27717809.14678073</t>
+          <t>27717809.14678061</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="CP42" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ42" t="inlineStr">
@@ -21313,12 +21313,12 @@
       </c>
       <c r="CX42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -21594,12 +21594,12 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>-88.70</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -21635,12 +21635,12 @@
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>1345904.751968676</t>
+          <t>1345904.75196812</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>-1550904.26186499</t>
+          <t>-1550904.261865109</t>
         </is>
       </c>
       <c r="BQ43" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="CP43" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ43" t="inlineStr">
@@ -21810,12 +21810,12 @@
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -21877,7 +21877,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -22091,12 +22091,12 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-89.82</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
@@ -22132,12 +22132,12 @@
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>1872597.299938434</t>
+          <t>1872597.299937798</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>1734703.449422061</t>
+          <t>1734703.449421912</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="CP44" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ44" t="inlineStr">
@@ -22307,12 +22307,12 @@
       </c>
       <c r="CX44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
@@ -22588,12 +22588,12 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>-91.17</t>
+          <t>-91.29</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>226837202.1334662</t>
+          <t>277124511.4931102</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
@@ -22629,12 +22629,12 @@
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>1897668.909123229</t>
+          <t>1897668.909122505</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>3732609.306638479</t>
+          <t>3732609.30663833</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="CP45" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ45" t="inlineStr">
@@ -22804,12 +22804,12 @@
       </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -22966,12 +22966,12 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="BO46" t="inlineStr">
         <is>
-          <t>-30517724.78436583</t>
+          <t>-30517724.78436559</t>
         </is>
       </c>
       <c r="BP46" t="inlineStr">
@@ -23301,12 +23301,12 @@
       </c>
       <c r="CX46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -23463,12 +23463,12 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -23623,7 +23623,7 @@
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>170031730.1002144</t>
+          <t>170031730.1002147</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
@@ -23798,12 +23798,12 @@
       </c>
       <c r="CX47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -23960,12 +23960,12 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -24056,7 +24056,7 @@
         </is>
       </c>
       <c r="AZ48" t="n">
-        <v>71.8</v>
+        <v>71.81</v>
       </c>
       <c r="BA48" t="n">
         <v>64.16</v>
@@ -24094,7 +24094,7 @@
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>402127393.5617275</t>
+          <t>402127393.5617278</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
@@ -24295,12 +24295,12 @@
       </c>
       <c r="CX48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -24457,12 +24457,12 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>639260934.1630212</t>
+          <t>639260934.1630217</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
@@ -24792,12 +24792,12 @@
       </c>
       <c r="CX49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -24954,12 +24954,12 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>866532702.6239387</t>
+          <t>866532702.6239393</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
@@ -25289,12 +25289,12 @@
       </c>
       <c r="CX50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>1049896627.348487</t>
+          <t>1049896627.348488</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
@@ -25786,12 +25786,12 @@
       </c>
       <c r="CX51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -25948,12 +25948,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -26082,7 +26082,7 @@
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>1182371602.913869</t>
+          <t>1182371602.91387</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
@@ -26283,12 +26283,12 @@
       </c>
       <c r="CX52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -26445,12 +26445,12 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -26475,7 +26475,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
@@ -26605,7 +26605,7 @@
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>1301117726.866077</t>
+          <t>1301117726.866078</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
@@ -26780,12 +26780,12 @@
       </c>
       <c r="CX53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -26942,12 +26942,12 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
@@ -27102,7 +27102,7 @@
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>1350822801.567147</t>
+          <t>1350822801.567148</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
@@ -27277,12 +27277,12 @@
       </c>
       <c r="CX54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -27439,12 +27439,12 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
@@ -27573,7 +27573,7 @@
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>1404163122.003942</t>
+          <t>1404163122.003943</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="CX55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -27936,12 +27936,12 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>4781639005.834661</t>
+          <t>2775719625.66437</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>1365520284.344708</t>
+          <t>1365520284.34471</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
@@ -28271,12 +28271,12 @@
       </c>
       <c r="CX56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28338,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr">
@@ -28593,12 +28593,12 @@
       </c>
       <c r="BO57" t="inlineStr">
         <is>
-          <t>294469376.0577447</t>
+          <t>294469376.0577477</t>
         </is>
       </c>
       <c r="BP57" t="inlineStr">
         <is>
-          <t>7169135.173614025</t>
+          <t>7169135.173614502</t>
         </is>
       </c>
       <c r="BQ57" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="BR57" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS57" t="inlineStr">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="CP57" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ57" t="inlineStr">
@@ -28768,12 +28768,12 @@
       </c>
       <c r="CX57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
@@ -29022,7 +29022,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>47.42999999999999</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AZ58" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr">
@@ -29090,12 +29090,12 @@
       </c>
       <c r="BO58" t="inlineStr">
         <is>
-          <t>346705783.491223</t>
+          <t>346705783.4912265</t>
         </is>
       </c>
       <c r="BP58" t="inlineStr">
         <is>
-          <t>139286794.8164153</t>
+          <t>139286794.8164158</t>
         </is>
       </c>
       <c r="BQ58" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="BR58" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS58" t="inlineStr">
@@ -29225,7 +29225,7 @@
       </c>
       <c r="CP58" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ58" t="inlineStr">
@@ -29265,12 +29265,12 @@
       </c>
       <c r="CX58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -29332,7 +29332,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr">
@@ -29587,12 +29587,12 @@
       </c>
       <c r="BO59" t="inlineStr">
         <is>
-          <t>384418326.8866426</t>
+          <t>384418326.8866466</t>
         </is>
       </c>
       <c r="BP59" t="inlineStr">
         <is>
-          <t>325387020.0626879</t>
+          <t>325387020.0626884</t>
         </is>
       </c>
       <c r="BQ59" t="inlineStr">
@@ -29602,7 +29602,7 @@
       </c>
       <c r="BR59" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS59" t="inlineStr">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="CP59" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ59" t="inlineStr">
@@ -29762,12 +29762,12 @@
       </c>
       <c r="CX59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -29829,7 +29829,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -29839,7 +29839,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
@@ -30058,7 +30058,7 @@
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="BO60" t="inlineStr">
         <is>
-          <t>395151291.7637253</t>
+          <t>395151291.7637299</t>
         </is>
       </c>
       <c r="BP60" t="inlineStr">
         <is>
-          <t>486836532.2336955</t>
+          <t>486836532.2336965</t>
         </is>
       </c>
       <c r="BQ60" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="BR60" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS60" t="inlineStr">
@@ -30219,7 +30219,7 @@
       </c>
       <c r="CP60" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ60" t="inlineStr">
@@ -30259,12 +30259,12 @@
       </c>
       <c r="CX60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -30336,7 +30336,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
@@ -30513,7 +30513,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>48.95999999999999</t>
         </is>
       </c>
       <c r="AZ61" t="n">
@@ -30555,7 +30555,7 @@
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr">
@@ -30581,12 +30581,12 @@
       </c>
       <c r="BO61" t="inlineStr">
         <is>
-          <t>378481248.0419125</t>
+          <t>378481248.0419178</t>
         </is>
       </c>
       <c r="BP61" t="inlineStr">
         <is>
-          <t>675474063.2553601</t>
+          <t>675474063.2553611</t>
         </is>
       </c>
       <c r="BQ61" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="BR61" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS61" t="inlineStr">
@@ -30716,7 +30716,7 @@
       </c>
       <c r="CP61" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ61" t="inlineStr">
@@ -30756,12 +30756,12 @@
       </c>
       <c r="CX61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -30823,7 +30823,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr">
@@ -31078,12 +31078,12 @@
       </c>
       <c r="BO62" t="inlineStr">
         <is>
-          <t>324482554.3667402</t>
+          <t>324482554.3667463</t>
         </is>
       </c>
       <c r="BP62" t="inlineStr">
         <is>
-          <t>818230695.0629044</t>
+          <t>818230695.0629053</t>
         </is>
       </c>
       <c r="BQ62" t="inlineStr">
@@ -31093,7 +31093,7 @@
       </c>
       <c r="BR62" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS62" t="inlineStr">
@@ -31213,7 +31213,7 @@
       </c>
       <c r="CP62" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ62" t="inlineStr">
@@ -31253,12 +31253,12 @@
       </c>
       <c r="CX62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
@@ -31507,7 +31507,7 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>45.92999999999999</t>
         </is>
       </c>
       <c r="AZ63" t="n">
@@ -31549,7 +31549,7 @@
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr">
@@ -31575,12 +31575,12 @@
       </c>
       <c r="BO63" t="inlineStr">
         <is>
-          <t>234710165.1492558</t>
+          <t>234710165.1492628</t>
         </is>
       </c>
       <c r="BP63" t="inlineStr">
         <is>
-          <t>820220731.6071486</t>
+          <t>820220731.6071501</t>
         </is>
       </c>
       <c r="BQ63" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="BR63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS63" t="inlineStr">
@@ -31710,7 +31710,7 @@
       </c>
       <c r="CP63" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ63" t="inlineStr">
@@ -31750,12 +31750,12 @@
       </c>
       <c r="CX63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -31817,7 +31817,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>44.20999999999999</t>
         </is>
       </c>
       <c r="AZ64" t="n">
@@ -32046,7 +32046,7 @@
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr">
@@ -32072,12 +32072,12 @@
       </c>
       <c r="BO64" t="inlineStr">
         <is>
-          <t>128253698.520548</t>
+          <t>128253698.5205561</t>
         </is>
       </c>
       <c r="BP64" t="inlineStr">
         <is>
-          <t>285648022.9343855</t>
+          <t>285648022.9343872</t>
         </is>
       </c>
       <c r="BQ64" t="inlineStr">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="BR64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS64" t="inlineStr">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="CP64" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ64" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="CX64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -32314,7 +32314,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -32324,7 +32324,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -32439,7 +32439,7 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
@@ -32543,7 +32543,7 @@
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr">
@@ -32569,12 +32569,12 @@
       </c>
       <c r="BO65" t="inlineStr">
         <is>
-          <t>99636548.62712297</t>
+          <t>99636548.6271322</t>
         </is>
       </c>
       <c r="BP65" t="inlineStr">
         <is>
-          <t>90644112.83278227</t>
+          <t>90644112.83278418</t>
         </is>
       </c>
       <c r="BQ65" t="inlineStr">
@@ -32584,7 +32584,7 @@
       </c>
       <c r="BR65" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS65" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="CP65" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ65" t="inlineStr">
@@ -32744,12 +32744,12 @@
       </c>
       <c r="CX65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -32811,7 +32811,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -32821,7 +32821,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="BO66" t="inlineStr">
         <is>
-          <t>101271536.9533667</t>
+          <t>101271536.9533773</t>
         </is>
       </c>
       <c r="BP66" t="inlineStr">
         <is>
-          <t>46238124.08646393</t>
+          <t>46238124.08646607</t>
         </is>
       </c>
       <c r="BQ66" t="inlineStr">
@@ -33081,7 +33081,7 @@
       </c>
       <c r="BR66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS66" t="inlineStr">
@@ -33201,7 +33201,7 @@
       </c>
       <c r="CP66" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ66" t="inlineStr">
@@ -33241,12 +33241,12 @@
       </c>
       <c r="CX66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-02-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -33433,7 +33433,7 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
@@ -33495,7 +33495,7 @@
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>42.70999999999999</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AZ67" t="n">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>1420767183.558</t>
+          <t>1249068541.366864</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr">
@@ -33563,12 +33563,12 @@
       </c>
       <c r="BO67" t="inlineStr">
         <is>
-          <t>111277612.0200763</t>
+          <t>111277612.0200884</t>
         </is>
       </c>
       <c r="BP67" t="inlineStr">
         <is>
-          <t>33297444.83863521</t>
+          <t>33297444.83863783</t>
         </is>
       </c>
       <c r="BQ67" t="inlineStr">
@@ -33578,7 +33578,7 @@
       </c>
       <c r="BR67" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="BS67" t="inlineStr">
@@ -33698,7 +33698,7 @@
       </c>
       <c r="CP67" t="inlineStr">
         <is>
-          <t>塑膠工業右上上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ67" t="inlineStr">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="CX67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
